--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.14967757071273</v>
+        <v>5.549322605240818</v>
       </c>
       <c r="D2" t="n">
-        <v>34.36849405324089</v>
+        <v>5.584880283651644</v>
       </c>
       <c r="E2" t="n">
-        <v>7.906465689720117</v>
+        <v>1.284800674579519</v>
       </c>
       <c r="F2" t="n">
-        <v>6.91918550425887</v>
+        <v>1.124367644442066</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.68061915101776</v>
+        <v>5.148100612040386</v>
       </c>
       <c r="D3" t="n">
-        <v>30.90491587736181</v>
+        <v>5.022048830071295</v>
       </c>
       <c r="E3" t="n">
-        <v>7.906465689720117</v>
+        <v>1.284800674579519</v>
       </c>
       <c r="F3" t="n">
-        <v>6.91918550425887</v>
+        <v>1.124367644442066</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.18378770540715</v>
+        <v>2.304865502128662</v>
       </c>
       <c r="D4" t="n">
-        <v>14.58115393767998</v>
+        <v>2.369437514872997</v>
       </c>
       <c r="E4" t="n">
-        <v>7.906465689720117</v>
+        <v>1.284800674579519</v>
       </c>
       <c r="F4" t="n">
-        <v>6.91918550425887</v>
+        <v>1.124367644442066</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.77384496448965</v>
+        <v>5.325749806729568</v>
       </c>
       <c r="D5" t="n">
-        <v>37.0541240897538</v>
+        <v>6.021295164584992</v>
       </c>
       <c r="E5" t="n">
-        <v>7.906465689720117</v>
+        <v>1.284800674579519</v>
       </c>
       <c r="F5" t="n">
-        <v>6.91918550425887</v>
+        <v>1.124367644442066</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.00781059358212</v>
+        <v>2.601269221457095</v>
       </c>
       <c r="D6" t="n">
-        <v>29.717786049285</v>
+        <v>4.829140233008812</v>
       </c>
       <c r="E6" t="n">
-        <v>7.906465689720117</v>
+        <v>1.284800674579519</v>
       </c>
       <c r="F6" t="n">
-        <v>6.91918550425887</v>
+        <v>1.124367644442066</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.17278184538625</v>
+        <v>2.953077049875265</v>
       </c>
       <c r="D7" t="n">
-        <v>38.78416461896369</v>
+        <v>6.3024267505816</v>
       </c>
       <c r="E7" t="n">
-        <v>7.906465689720117</v>
+        <v>1.284800674579519</v>
       </c>
       <c r="F7" t="n">
-        <v>6.91918550425887</v>
+        <v>1.124367644442066</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.71055511742746</v>
+        <v>4.990465206581963</v>
       </c>
       <c r="D8" t="n">
-        <v>31.57507507387323</v>
+        <v>5.130949699504399</v>
       </c>
       <c r="E8" t="n">
-        <v>7.906465689720117</v>
+        <v>1.284800674579519</v>
       </c>
       <c r="F8" t="n">
-        <v>6.91918550425887</v>
+        <v>1.124367644442066</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.73178545341337</v>
+        <v>5.156415136179672</v>
       </c>
       <c r="D9" t="n">
-        <v>32.80155330055096</v>
+        <v>5.330252411339531</v>
       </c>
       <c r="E9" t="n">
-        <v>7.906465689720117</v>
+        <v>1.284800674579519</v>
       </c>
       <c r="F9" t="n">
-        <v>6.91918550425887</v>
+        <v>1.124367644442066</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
